--- a/artfynd/A 30335-2025 artfynd.xlsx
+++ b/artfynd/A 30335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117865442</v>
+        <v>117865422</v>
       </c>
       <c r="B2" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552159</v>
+        <v>552680</v>
       </c>
       <c r="R2" t="n">
-        <v>7010093</v>
+        <v>7009892</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117865419</v>
+        <v>117865435</v>
       </c>
       <c r="B3" t="n">
-        <v>97744</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552680</v>
+        <v>552379</v>
       </c>
       <c r="R3" t="n">
-        <v>7009892</v>
+        <v>7009918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117865416</v>
+        <v>117865442</v>
       </c>
       <c r="B4" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552680</v>
+        <v>552159</v>
       </c>
       <c r="R4" t="n">
-        <v>7009892</v>
+        <v>7010093</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117865446</v>
+        <v>117865440</v>
       </c>
       <c r="B5" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552419</v>
+        <v>552243</v>
       </c>
       <c r="R5" t="n">
-        <v>7010121</v>
+        <v>7010051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117865418</v>
+        <v>117865434</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552680</v>
+        <v>552379</v>
       </c>
       <c r="R6" t="n">
-        <v>7009892</v>
+        <v>7009918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,43 +1160,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117865421</v>
+        <v>117865418</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storklinsen, Jmt</t>
@@ -1266,18 +1233,12 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på björk</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,12 +1260,7 @@
         <v>117865428</v>
       </c>
       <c r="B8" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117865415</v>
+        <v>117865421</v>
       </c>
       <c r="B9" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,24 +1365,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storklinsen, Jmt</t>
@@ -1444,7 +1398,7 @@
         <v>7009892</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1476,12 +1430,18 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på björk</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1500,37 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117865443</v>
+        <v>117865419</v>
       </c>
       <c r="B10" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552159</v>
+        <v>552680</v>
       </c>
       <c r="R10" t="n">
-        <v>7010093</v>
+        <v>7009892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,37 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117865417</v>
+        <v>117865416</v>
       </c>
       <c r="B11" t="n">
-        <v>104919</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,7 +1598,7 @@
         <v>7009892</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,37 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117865422</v>
+        <v>117865443</v>
       </c>
       <c r="B12" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552680</v>
+        <v>552159</v>
       </c>
       <c r="R12" t="n">
-        <v>7009892</v>
+        <v>7010093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,6 +1748,200 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>117865446</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storklinsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552419</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7010121</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>117865417</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storklinsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552680</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7009892</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30335-2025 artfynd.xlsx
+++ b/artfynd/A 30335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865434</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865421</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865419</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865416</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865443</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865446</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,8 +2007,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>